--- a/reports/20260515/UI_LOGIN_RESTRICTION_PW.xlsx
+++ b/reports/20260515/UI_LOGIN_RESTRICTION_PW.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>62.09</v>
+        <v>58.72</v>
       </c>
       <c r="E2" t="n">
         <v>7</v>
